--- a/Feuilles/Regrets.xlsx
+++ b/Feuilles/Regrets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA47F025-49F9-E94C-AA02-0C4C5861E9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21B0996-E0B6-864E-B59F-1EEFA98AEC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="2240" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>MES</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>END</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -455,10 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -486,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -497,7 +503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -508,7 +514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -519,7 +525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -530,7 +536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -541,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -552,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -563,7 +569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -574,7 +580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -585,7 +591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -596,7 +602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -607,7 +613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -621,7 +627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -632,7 +638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Regrets.xlsx
+++ b/Feuilles/Regrets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21B0996-E0B6-864E-B59F-1EEFA98AEC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928B07C9-0780-AF4D-A4B3-39598C1DFD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="2240" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1213,8 +1213,11 @@
       <c r="D66" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1225,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1247,7 +1250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1258,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1269,7 +1272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1280,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1304,8 +1307,11 @@
       <c r="D74" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1327,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1338,7 +1344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1349,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1360,7 +1366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1371,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1382,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1395,8 +1401,11 @@
       <c r="D82" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1407,7 +1416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1418,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1429,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1440,7 +1449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1451,7 +1460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1462,7 +1471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1473,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1483,8 +1492,11 @@
       <c r="C90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1495,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1506,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1517,7 +1529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1528,7 +1540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1539,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1550,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1561,7 +1573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1574,8 +1586,11 @@
       <c r="D98" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1586,7 +1601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1597,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1608,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1619,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1630,7 +1645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1641,7 +1656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1652,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1662,8 +1677,11 @@
       <c r="C106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1674,7 +1692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1685,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1696,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1710,7 +1728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1721,7 +1739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>

--- a/Feuilles/Regrets.xlsx
+++ b/Feuilles/Regrets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928B07C9-0780-AF4D-A4B3-39598C1DFD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B848FF-387A-7148-AE68-B9F838D99FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="2240" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>MES</t>
   </si>
@@ -65,9 +65,6 @@
     <t>PONT</t>
   </si>
   <si>
-    <t>REFRAIN 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">COUPLET 2 </t>
   </si>
   <si>
@@ -87,6 +84,12 @@
   </si>
   <si>
     <t>LOOP</t>
+  </si>
+  <si>
+    <t>REFRAIN 3a</t>
+  </si>
+  <si>
+    <t>REFRAIN 3b</t>
   </si>
 </sst>
 </file>
@@ -475,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -715,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1120,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -1211,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -1305,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -1399,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -1492,6 +1495,9 @@
       <c r="C90">
         <v>0</v>
       </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
       <c r="E90">
         <v>1</v>
       </c>
@@ -1584,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -1677,9 +1683,6 @@
       <c r="C106">
         <v>0</v>
       </c>
-      <c r="E106">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
@@ -1725,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
